--- a/docs/downloads/05/tbl_agri_equip_alaotra_mangabe.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_mangabe.xlsx
@@ -436,12 +436,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -472,12 +460,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -526,12 +508,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -580,12 +556,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -598,12 +568,6 @@
           <t>Herse/Pulvériseur/Rotovat</t>
         </is>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -616,12 +580,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,12 +592,6 @@
           <t>Natte et semblables (goel</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -724,12 +676,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -791,12 +737,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -809,12 +749,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -827,12 +761,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -863,12 +791,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -899,12 +821,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -917,12 +833,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -935,12 +845,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -989,12 +893,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1187,12 +1085,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1241,12 +1133,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1259,12 +1145,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C51">
-        <v>3</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1276,12 +1156,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
       </c>
     </row>
     <row r="53">
